--- a/data/MLB/2026年/公式戦/raw/2026-08-26/highlights_20260826.xlsx
+++ b/data/MLB/2026年/公式戦/raw/2026-08-26/highlights_20260826.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,216 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ライアン・ワルドシュミット</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>waldschmidt, ryan</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ダイヤモンドバックス</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>打者</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9回裏にウェブ（カブス）から逆転サヨナラ2ランを放ち、劇的な勝利を呼び込んだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>オニール・クルーズ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cruz, oneil</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>パイレーツ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>打者</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9回表にミラー（パドレス）から決勝ソロホームランを放ち、チームを勝利に導いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ヤイナー・ディアス</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>diaz, yainer</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>アストロズ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>打者</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2本塁打を放ち、特に8回にはウォーレン（ヤンキース）から同点ソロを放つ活躍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ホセ・ラミレス</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ramírez, josé</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ガーディアンズ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>打者</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8回に同点二塁打、延長10回には勝ち越し二塁打を放ち、猛打賞の活躍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ジョージ・カービー</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kirby, george</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>マリナーズ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>投手</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>フィリーズ相手に7.2回を投げ、1失点9奪三振の快投で試合を支配した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ポール・スキーンズ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>skenes, paul</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>パイレーツ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>投手</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>パドレス相手に6回を無失点4奪三振に抑え、投手戦を演じた。</t>
         </is>
       </c>
     </row>
